--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/180.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/180.xlsx
@@ -426,13 +426,13 @@
         <v>3.933481835567745</v>
       </c>
       <c r="E2">
-        <v>-11.64592849544754</v>
+        <v>-10.17630735421229</v>
       </c>
       <c r="F2">
-        <v>-1.612625217014848</v>
+        <v>-1.736999612340777</v>
       </c>
       <c r="G2">
-        <v>-4.603248512114134</v>
+        <v>-2.833252097360637</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>3.876331051135952</v>
       </c>
       <c r="E3">
-        <v>-10.8502982546699</v>
+        <v>-10.64071594912091</v>
       </c>
       <c r="F3">
-        <v>-2.375024753325012</v>
+        <v>-1.862180837517033</v>
       </c>
       <c r="G3">
-        <v>-4.927096008402259</v>
+        <v>-3.60285130832947</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>3.76441920496066</v>
       </c>
       <c r="E4">
-        <v>-12.49776162713438</v>
+        <v>-10.53220465494911</v>
       </c>
       <c r="F4">
-        <v>-1.894240312740179</v>
+        <v>-1.998851518570118</v>
       </c>
       <c r="G4">
-        <v>-4.130880011297686</v>
+        <v>-3.014107200171022</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>3.612956458932219</v>
       </c>
       <c r="E5">
-        <v>-14.66306505932399</v>
+        <v>-12.38701779527681</v>
       </c>
       <c r="F5">
-        <v>-2.310183466503478</v>
+        <v>-1.929054109577634</v>
       </c>
       <c r="G5">
-        <v>-4.105014718999359</v>
+        <v>-2.924030566592992</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>3.444015040045558</v>
       </c>
       <c r="E6">
-        <v>-12.97791572616767</v>
+        <v>-12.30984354123809</v>
       </c>
       <c r="F6">
-        <v>-2.286989179225092</v>
+        <v>-1.771189648523924</v>
       </c>
       <c r="G6">
-        <v>-4.573039784068285</v>
+        <v>-3.066721700426659</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>3.282189148121642</v>
       </c>
       <c r="E7">
-        <v>-13.97935152517191</v>
+        <v>-13.3873667605192</v>
       </c>
       <c r="F7">
-        <v>-2.660703819528478</v>
+        <v>-1.275865703285154</v>
       </c>
       <c r="G7">
-        <v>-4.254492471188533</v>
+        <v>-1.723434742411982</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>3.145423495149779</v>
       </c>
       <c r="E8">
-        <v>-15.88933506433505</v>
+        <v>-13.60775853352451</v>
       </c>
       <c r="F8">
-        <v>-2.627900470377617</v>
+        <v>-1.811125241012888</v>
       </c>
       <c r="G8">
-        <v>-3.511033327797784</v>
+        <v>-1.969123569063454</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>3.053562530756415</v>
       </c>
       <c r="E9">
-        <v>-14.83736149540521</v>
+        <v>-14.7405291356992</v>
       </c>
       <c r="F9">
-        <v>-2.76810662350585</v>
+        <v>-2.030003931487199</v>
       </c>
       <c r="G9">
-        <v>-4.544108926600593</v>
+        <v>-1.270618323550469</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>3.023622357738657</v>
       </c>
       <c r="E10">
-        <v>-15.46551518195718</v>
+        <v>-15.44410908532293</v>
       </c>
       <c r="F10">
-        <v>-2.29967976783598</v>
+        <v>-2.089597510811998</v>
       </c>
       <c r="G10">
-        <v>-3.42093020985544</v>
+        <v>-0.3860372449116685</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>3.062624094721164</v>
       </c>
       <c r="E11">
-        <v>-16.22584596784504</v>
+        <v>-15.79038337879345</v>
       </c>
       <c r="F11">
-        <v>-2.420744007020323</v>
+        <v>-2.053479035315134</v>
       </c>
       <c r="G11">
-        <v>-1.792674802365839</v>
+        <v>-0.5723713005895472</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>3.167185687970776</v>
       </c>
       <c r="E12">
-        <v>-16.94596390454478</v>
+        <v>-16.59401543314264</v>
       </c>
       <c r="F12">
-        <v>-2.387219978229027</v>
+        <v>-2.200369285016556</v>
       </c>
       <c r="G12">
-        <v>-2.051662090448563</v>
+        <v>-0.4465242224596924</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>3.33084480971554</v>
       </c>
       <c r="E13">
-        <v>-18.23517516978845</v>
+        <v>-16.78274864436032</v>
       </c>
       <c r="F13">
-        <v>-2.168743874312477</v>
+        <v>-1.968923432674374</v>
       </c>
       <c r="G13">
-        <v>-0.94792289711001</v>
+        <v>1.257443361513041</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>3.546039813230041</v>
       </c>
       <c r="E14">
-        <v>-19.54404906917343</v>
+        <v>-17.47702257989829</v>
       </c>
       <c r="F14">
-        <v>-3.070256118779179</v>
+        <v>-1.888312515605746</v>
       </c>
       <c r="G14">
-        <v>-0.7157675806230788</v>
+        <v>0.731563202599813</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>3.796609775955202</v>
       </c>
       <c r="E15">
-        <v>-19.56352150740641</v>
+        <v>-18.32150599827068</v>
       </c>
       <c r="F15">
-        <v>-2.446137609753142</v>
+        <v>-2.259143608979987</v>
       </c>
       <c r="G15">
-        <v>-1.324116739465091</v>
+        <v>1.670937120459091</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>4.065447439643818</v>
       </c>
       <c r="E16">
-        <v>-20.03169779268941</v>
+        <v>-19.56243014517056</v>
       </c>
       <c r="F16">
-        <v>-1.983448855082464</v>
+        <v>-1.922678165678286</v>
       </c>
       <c r="G16">
-        <v>-0.2546350713669165</v>
+        <v>2.704949603649514</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>4.337735036672829</v>
       </c>
       <c r="E17">
-        <v>-20.71036660679695</v>
+        <v>-20.41493801948455</v>
       </c>
       <c r="F17">
-        <v>-2.313669236534459</v>
+        <v>-1.745256778611882</v>
       </c>
       <c r="G17">
-        <v>0.7098559554988119</v>
+        <v>2.649646940415989</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>4.598596701169168</v>
       </c>
       <c r="E18">
-        <v>-21.76989367037158</v>
+        <v>-22.38348378451488</v>
       </c>
       <c r="F18">
-        <v>-1.539980709258943</v>
+        <v>-1.885494409701422</v>
       </c>
       <c r="G18">
-        <v>1.582111873094906</v>
+        <v>3.115821410528461</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>4.82771254290064</v>
       </c>
       <c r="E19">
-        <v>-22.46129202491467</v>
+        <v>-20.58043110209486</v>
       </c>
       <c r="F19">
-        <v>-1.582528972536337</v>
+        <v>-1.691658094181143</v>
       </c>
       <c r="G19">
-        <v>0.1786458182673571</v>
+        <v>2.853761936185293</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>5.007668763831704</v>
       </c>
       <c r="E20">
-        <v>-23.88441026656516</v>
+        <v>-22.45855229814003</v>
       </c>
       <c r="F20">
-        <v>-1.762048614234031</v>
+        <v>-1.453754289566737</v>
       </c>
       <c r="G20">
-        <v>0.7646852107202212</v>
+        <v>3.701053029869743</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>5.124820135241175</v>
       </c>
       <c r="E21">
-        <v>-23.47518565591401</v>
+        <v>-22.69934484654989</v>
       </c>
       <c r="F21">
-        <v>-1.126173915027464</v>
+        <v>-1.232890830795318</v>
       </c>
       <c r="G21">
-        <v>1.541143872046425</v>
+        <v>3.247544706990523</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>5.168295364931018</v>
       </c>
       <c r="E22">
-        <v>-23.04672408767828</v>
+        <v>-23.6774408905186</v>
       </c>
       <c r="F22">
-        <v>-1.049616199660733</v>
+        <v>-0.9534510278697387</v>
       </c>
       <c r="G22">
-        <v>1.585190680446428</v>
+        <v>4.145454041970429</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>5.128939693256951</v>
       </c>
       <c r="E23">
-        <v>-23.63997229657913</v>
+        <v>-23.89037426683326</v>
       </c>
       <c r="F23">
-        <v>-1.209658438616403</v>
+        <v>-0.8910600518256856</v>
       </c>
       <c r="G23">
-        <v>0.6358354677862473</v>
+        <v>4.644234075099183</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>5.003422186424135</v>
       </c>
       <c r="E24">
-        <v>-24.84833218688986</v>
+        <v>-24.01584469616379</v>
       </c>
       <c r="F24">
-        <v>-0.4190910971414448</v>
+        <v>-1.014962277732019</v>
       </c>
       <c r="G24">
-        <v>2.544470908633343</v>
+        <v>4.473880022739366</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>4.795387499980853</v>
       </c>
       <c r="E25">
-        <v>-25.91439383845756</v>
+        <v>-25.38775495373553</v>
       </c>
       <c r="F25">
-        <v>-0.9159152157466847</v>
+        <v>-1.053152500103284</v>
       </c>
       <c r="G25">
-        <v>1.141133965081826</v>
+        <v>3.789457837950441</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>4.511103342850623</v>
       </c>
       <c r="E26">
-        <v>-27.35588862763117</v>
+        <v>-24.99274975146847</v>
       </c>
       <c r="F26">
-        <v>-0.9332786248767652</v>
+        <v>-1.027356310812705</v>
       </c>
       <c r="G26">
-        <v>2.765777567388083</v>
+        <v>2.965231315038094</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>4.159959466658607</v>
       </c>
       <c r="E27">
-        <v>-24.91450224908994</v>
+        <v>-24.54625127126019</v>
       </c>
       <c r="F27">
-        <v>-0.9914407853295268</v>
+        <v>-0.6593391815057742</v>
       </c>
       <c r="G27">
-        <v>0.02354675975250204</v>
+        <v>4.035236049331473</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>3.753925223931552</v>
       </c>
       <c r="E28">
-        <v>-24.52721356653194</v>
+        <v>-23.49027905978158</v>
       </c>
       <c r="F28">
-        <v>-0.7367144954990676</v>
+        <v>-1.056226571535073</v>
       </c>
       <c r="G28">
-        <v>1.128255942934062</v>
+        <v>3.017789536019563</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>3.312701969792283</v>
       </c>
       <c r="E29">
-        <v>-25.31963764771216</v>
+        <v>-24.09175097748036</v>
       </c>
       <c r="F29">
-        <v>-0.9463154710620237</v>
+        <v>-0.6525457404354155</v>
       </c>
       <c r="G29">
-        <v>1.024341229001878</v>
+        <v>2.993235219754788</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>2.854268801775065</v>
       </c>
       <c r="E30">
-        <v>-25.99469726803558</v>
+        <v>-23.61512455969904</v>
       </c>
       <c r="F30">
-        <v>-0.3774134480043933</v>
+        <v>-0.9946995826921401</v>
       </c>
       <c r="G30">
-        <v>1.165363847883752</v>
+        <v>2.409059664440534</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>2.396728391238547</v>
       </c>
       <c r="E31">
-        <v>-24.54939856069552</v>
+        <v>-23.07941061306565</v>
       </c>
       <c r="F31">
-        <v>-0.2268725831588335</v>
+        <v>-0.6530966047582771</v>
       </c>
       <c r="G31">
-        <v>1.135992687859338</v>
+        <v>2.198396409594551</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>1.959394882991671</v>
       </c>
       <c r="E32">
-        <v>-26.28715517639894</v>
+        <v>-23.45786424283467</v>
       </c>
       <c r="F32">
-        <v>-0.8524167124850887</v>
+        <v>-0.4768042824618892</v>
       </c>
       <c r="G32">
-        <v>0.5213865979481032</v>
+        <v>2.469841280541553</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>1.562470394408893</v>
       </c>
       <c r="E33">
-        <v>-23.47649891337624</v>
+        <v>-23.24811891222141</v>
       </c>
       <c r="F33">
-        <v>-0.4192915620529223</v>
+        <v>-0.7234142284797188</v>
       </c>
       <c r="G33">
-        <v>0.9765799885068128</v>
+        <v>2.290651382137421</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>1.21914369697285</v>
       </c>
       <c r="E34">
-        <v>-23.07978647640828</v>
+        <v>-21.87654376172623</v>
       </c>
       <c r="F34">
-        <v>-0.8886254800288578</v>
+        <v>-0.9320484992836079</v>
       </c>
       <c r="G34">
-        <v>1.18395256108676</v>
+        <v>1.847306434063763</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>0.9380664045507185</v>
       </c>
       <c r="E35">
-        <v>-25.09762468101211</v>
+        <v>-22.36355397040712</v>
       </c>
       <c r="F35">
-        <v>-0.1252053950784446</v>
+        <v>-0.6390632325874508</v>
       </c>
       <c r="G35">
-        <v>-0.05499593316670687</v>
+        <v>2.159530604963507</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>0.727281144255047</v>
       </c>
       <c r="E36">
-        <v>-22.85271973271568</v>
+        <v>-21.65178201130352</v>
       </c>
       <c r="F36">
-        <v>-0.523819102775178</v>
+        <v>-0.6739764335132415</v>
       </c>
       <c r="G36">
-        <v>0.6404437471769129</v>
+        <v>2.077177474128598</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>0.5898681111670067</v>
       </c>
       <c r="E37">
-        <v>-22.51402157625999</v>
+        <v>-21.85821249894317</v>
       </c>
       <c r="F37">
-        <v>-0.3968444621718613</v>
+        <v>-0.5806981221210031</v>
       </c>
       <c r="G37">
-        <v>-0.5999415238405977</v>
+        <v>1.368849840000595</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>0.5222000517893387</v>
       </c>
       <c r="E38">
-        <v>-22.02162248350996</v>
+        <v>-20.60623887546457</v>
       </c>
       <c r="F38">
-        <v>0.1955028434872036</v>
+        <v>-0.2562191551378116</v>
       </c>
       <c r="G38">
-        <v>0.03789797466524263</v>
+        <v>1.369776792751591</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>0.518837177664745</v>
       </c>
       <c r="E39">
-        <v>-21.02222902628318</v>
+        <v>-20.06042190332007</v>
       </c>
       <c r="F39">
-        <v>-0.7094777752950199</v>
+        <v>-0.2068675103812255</v>
       </c>
       <c r="G39">
-        <v>-0.4321167282727841</v>
+        <v>2.631660746501129</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>0.5753881985370385</v>
       </c>
       <c r="E40">
-        <v>-21.02968289449981</v>
+        <v>-19.94700627179796</v>
       </c>
       <c r="F40">
-        <v>-1.015389715311863</v>
+        <v>-0.4528536957447471</v>
       </c>
       <c r="G40">
-        <v>-0.2454185125855856</v>
+        <v>1.608218835217598</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>0.682158657643431</v>
       </c>
       <c r="E41">
-        <v>-18.80356205638719</v>
+        <v>-18.70555682191319</v>
       </c>
       <c r="F41">
-        <v>-0.05720388661523041</v>
+        <v>-0.2391572717423502</v>
       </c>
       <c r="G41">
-        <v>-0.3788632927280678</v>
+        <v>2.008023488358762</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>0.8264703640330232</v>
       </c>
       <c r="E42">
-        <v>-20.6199510947598</v>
+        <v>-17.02617676464264</v>
       </c>
       <c r="F42">
-        <v>-0.9350405623425198</v>
+        <v>-0.5782908864484678</v>
       </c>
       <c r="G42">
-        <v>0.01757453559965682</v>
+        <v>1.722631289054811</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>0.9951284933456298</v>
       </c>
       <c r="E43">
-        <v>-19.48953529906909</v>
+        <v>-18.67872561341774</v>
       </c>
       <c r="F43">
-        <v>-0.5468079549376698</v>
+        <v>-0.2471576441185878</v>
       </c>
       <c r="G43">
-        <v>-0.7496774985818335</v>
+        <v>1.592927425371705</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>1.175308812383376</v>
       </c>
       <c r="E44">
-        <v>-19.39018510781482</v>
+        <v>-16.97962405184379</v>
       </c>
       <c r="F44">
-        <v>-0.2243129278841831</v>
+        <v>-0.09853859164752295</v>
       </c>
       <c r="G44">
-        <v>-0.963134853862961</v>
+        <v>2.19762836302944</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>1.351611978286</v>
       </c>
       <c r="E45">
-        <v>-18.33150486887962</v>
+        <v>-16.87773791514521</v>
       </c>
       <c r="F45">
-        <v>-0.1367917699414013</v>
+        <v>-0.3405560687842321</v>
       </c>
       <c r="G45">
-        <v>0.4729367639808693</v>
+        <v>1.701119364140626</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>1.509575372129191</v>
       </c>
       <c r="E46">
-        <v>-17.34464622770607</v>
+        <v>-15.89364617159035</v>
       </c>
       <c r="F46">
-        <v>-0.06258910310083</v>
+        <v>-0.1939184711406636</v>
       </c>
       <c r="G46">
-        <v>-0.3982366052238828</v>
+        <v>1.79049416206433</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>1.636561091200047</v>
       </c>
       <c r="E47">
-        <v>-16.42587319323784</v>
+        <v>-15.9638103478652</v>
       </c>
       <c r="F47">
-        <v>-0.3086456996935896</v>
+        <v>-0.6750458558302557</v>
       </c>
       <c r="G47">
-        <v>-0.05192374690626321</v>
+        <v>1.061108147761024</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>1.721562953198506</v>
       </c>
       <c r="E48">
-        <v>-14.78740337015259</v>
+        <v>-15.48050443092257</v>
       </c>
       <c r="F48">
-        <v>0.1867826198379332</v>
+        <v>-0.4406518439015104</v>
       </c>
       <c r="G48">
-        <v>-0.6921269749271431</v>
+        <v>1.196198269036524</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>1.756001901763751</v>
       </c>
       <c r="E49">
-        <v>-17.2154896205333</v>
+        <v>-15.21409883352533</v>
       </c>
       <c r="F49">
-        <v>-0.1417412651731284</v>
+        <v>-0.04999129163905511</v>
       </c>
       <c r="G49">
-        <v>-0.202868070769333</v>
+        <v>1.372958227014831</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>1.734509464063893</v>
       </c>
       <c r="E50">
-        <v>-12.79460762681119</v>
+        <v>-13.09184760372665</v>
       </c>
       <c r="F50">
-        <v>0.4749037131448516</v>
+        <v>0.05031903063554822</v>
       </c>
       <c r="G50">
-        <v>-1.404357742245946</v>
+        <v>1.761146175858691</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>1.655306985525861</v>
       </c>
       <c r="E51">
-        <v>-15.52770924397853</v>
+        <v>-13.8348796189052</v>
       </c>
       <c r="F51">
-        <v>-0.7256640743457222</v>
+        <v>-0.276458655890412</v>
       </c>
       <c r="G51">
-        <v>-1.291239711714589</v>
+        <v>0.0956603732344463</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>1.519964336885274</v>
       </c>
       <c r="E52">
-        <v>-13.29937398207616</v>
+        <v>-12.87059089218589</v>
       </c>
       <c r="F52">
-        <v>-0.09907040352012023</v>
+        <v>-0.0681068583708775</v>
       </c>
       <c r="G52">
-        <v>-0.8036393908719538</v>
+        <v>1.43101195359149</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>1.333705982286331</v>
       </c>
       <c r="E53">
-        <v>-12.67921758062174</v>
+        <v>-11.87328958995065</v>
       </c>
       <c r="F53">
-        <v>-0.02953227352471293</v>
+        <v>-0.1869742672029954</v>
       </c>
       <c r="G53">
-        <v>-1.14088466495751</v>
+        <v>1.394334419561905</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>1.102836252275447</v>
       </c>
       <c r="E54">
-        <v>-12.79961159058966</v>
+        <v>-11.94761996231255</v>
       </c>
       <c r="F54">
-        <v>0.2279069195499146</v>
+        <v>-0.2292723635247437</v>
       </c>
       <c r="G54">
-        <v>-1.928370753475025</v>
+        <v>0.4276087744571682</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>0.8372904323216313</v>
       </c>
       <c r="E55">
-        <v>-11.94456777083138</v>
+        <v>-12.47147383551986</v>
       </c>
       <c r="F55">
-        <v>0.06648959070559736</v>
+        <v>-0.1006418164832309</v>
       </c>
       <c r="G55">
-        <v>-1.291680014271312</v>
+        <v>0.1327252410921265</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>0.5485199027863341</v>
       </c>
       <c r="E56">
-        <v>-12.64401322368611</v>
+        <v>-11.37988517597092</v>
       </c>
       <c r="F56">
-        <v>-0.0124927560491271</v>
+        <v>-0.4735579106103179</v>
       </c>
       <c r="G56">
-        <v>-2.648864642459849</v>
+        <v>0.02117640914638387</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>0.2484223674538457</v>
       </c>
       <c r="E57">
-        <v>-11.16061193604551</v>
+        <v>-10.3278074521389</v>
       </c>
       <c r="F57">
-        <v>0.2327321596712217</v>
+        <v>-0.2731708656687007</v>
       </c>
       <c r="G57">
-        <v>-2.49959876518519</v>
+        <v>-0.274869125702942</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-0.05296020927154548</v>
       </c>
       <c r="E58">
-        <v>-10.83453916512321</v>
+        <v>-11.09954999252609</v>
       </c>
       <c r="F58">
-        <v>-0.3073534465452223</v>
+        <v>-0.04475600965336224</v>
       </c>
       <c r="G58">
-        <v>-1.732624816828999</v>
+        <v>0.2928265339168204</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-0.3444029039291827</v>
       </c>
       <c r="E59">
-        <v>-10.86681359937588</v>
+        <v>-9.798397141324184</v>
       </c>
       <c r="F59">
-        <v>-0.2072386189776797</v>
+        <v>-0.1300844790809337</v>
       </c>
       <c r="G59">
-        <v>-1.841627839255042</v>
+        <v>0.1624274556704676</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-0.6164963407134098</v>
       </c>
       <c r="E60">
-        <v>-9.737040846994258</v>
+        <v>-10.82955331524076</v>
       </c>
       <c r="F60">
-        <v>0.321548884231982</v>
+        <v>-0.3055227545850354</v>
       </c>
       <c r="G60">
-        <v>-2.514843827393534</v>
+        <v>0.1284447057098489</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-0.8632385627288083</v>
       </c>
       <c r="E61">
-        <v>-11.28657596904287</v>
+        <v>-9.816778217321318</v>
       </c>
       <c r="F61">
-        <v>-0.1367793444303593</v>
+        <v>-0.3409338043199087</v>
       </c>
       <c r="G61">
-        <v>-1.607939740183428</v>
+        <v>-0.7239909757426284</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-1.080983718662414</v>
       </c>
       <c r="E62">
-        <v>-10.89060620181218</v>
+        <v>-9.45399310761883</v>
       </c>
       <c r="F62">
-        <v>0.2498611408263099</v>
+        <v>-0.2412397873929882</v>
       </c>
       <c r="G62">
-        <v>-2.372679070300611</v>
+        <v>-0.0360231966811437</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-1.267595694072615</v>
       </c>
       <c r="E63">
-        <v>-11.09807823847359</v>
+        <v>-8.621614300268943</v>
       </c>
       <c r="F63">
-        <v>0.2694296639826426</v>
+        <v>0.0866976134968913</v>
       </c>
       <c r="G63">
-        <v>-2.600911390323506</v>
+        <v>0.1198405978532831</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-1.42249077487721</v>
       </c>
       <c r="E64">
-        <v>-9.653689754409077</v>
+        <v>-8.528318678762918</v>
       </c>
       <c r="F64">
-        <v>0.3162879228568023</v>
+        <v>-0.09162669403856387</v>
       </c>
       <c r="G64">
-        <v>-1.496520019513717</v>
+        <v>0.1647647008211931</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-1.549494353566321</v>
       </c>
       <c r="E65">
-        <v>-11.56529448726697</v>
+        <v>-8.944960929838629</v>
       </c>
       <c r="F65">
-        <v>-0.3331512925706073</v>
+        <v>0.1288474320535385</v>
       </c>
       <c r="G65">
-        <v>-2.915201341639756</v>
+        <v>-0.2701383561273235</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-1.652751866160882</v>
       </c>
       <c r="E66">
-        <v>-9.899730804193824</v>
+        <v>-8.961467217596587</v>
       </c>
       <c r="F66">
-        <v>-0.6701286669272378</v>
+        <v>-0.06921769905803164</v>
       </c>
       <c r="G66">
-        <v>-3.074948406091748</v>
+        <v>0.4150353224990163</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-1.737319002683422</v>
       </c>
       <c r="E67">
-        <v>-10.12799759349846</v>
+        <v>-8.747374551935955</v>
       </c>
       <c r="F67">
-        <v>0.02787690095890401</v>
+        <v>-0.607025294916777</v>
       </c>
       <c r="G67">
-        <v>-2.153044237043204</v>
+        <v>-0.4401613539332132</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-1.807544877105412</v>
       </c>
       <c r="E68">
-        <v>-8.950064520045274</v>
+        <v>-8.22829821880674</v>
       </c>
       <c r="F68">
-        <v>-0.3475342357854151</v>
+        <v>-0.6809637125558553</v>
       </c>
       <c r="G68">
-        <v>-2.506663469365995</v>
+        <v>-0.3166713842273193</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-1.869570920545536</v>
       </c>
       <c r="E69">
-        <v>-9.225889343378467</v>
+        <v>-8.640611248731119</v>
       </c>
       <c r="F69">
-        <v>-0.3772386624824026</v>
+        <v>0.163671169299827</v>
       </c>
       <c r="G69">
-        <v>-2.903256893334065</v>
+        <v>0.05593382676319206</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-1.927667549768245</v>
       </c>
       <c r="E70">
-        <v>-9.327358860468337</v>
+        <v>-9.829503229282873</v>
       </c>
       <c r="F70">
-        <v>-0.2105429765474469</v>
+        <v>-0.3464424475485254</v>
       </c>
       <c r="G70">
-        <v>-2.977807068332913</v>
+        <v>-0.3664321942281045</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-1.98376122730527</v>
       </c>
       <c r="E71">
-        <v>-10.4373240675404</v>
+        <v>-8.327657467009036</v>
       </c>
       <c r="F71">
-        <v>-0.6581223097910618</v>
+        <v>-0.4951211424725919</v>
       </c>
       <c r="G71">
-        <v>-3.116214356238763</v>
+        <v>-0.3819255473518937</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-2.037655685243344</v>
       </c>
       <c r="E72">
-        <v>-11.57859008695349</v>
+        <v>-8.564818179264741</v>
       </c>
       <c r="F72">
-        <v>-0.8844662472994015</v>
+        <v>-1.116975723386778</v>
       </c>
       <c r="G72">
-        <v>-1.225485656213585</v>
+        <v>0.0705565064101529</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-2.089001467088563</v>
       </c>
       <c r="E73">
-        <v>-7.300309739732908</v>
+        <v>-8.469081710268581</v>
       </c>
       <c r="F73">
-        <v>-0.878634540783693</v>
+        <v>-1.077740101353179</v>
       </c>
       <c r="G73">
-        <v>-1.683529426481607</v>
+        <v>0.1456429897863627</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-2.136751839437367</v>
       </c>
       <c r="E74">
-        <v>-10.30381559684627</v>
+        <v>-10.05138034176269</v>
       </c>
       <c r="F74">
-        <v>-1.230992212708102</v>
+        <v>-1.217017654622874</v>
       </c>
       <c r="G74">
-        <v>-3.110281858632389</v>
+        <v>-0.2585415151032565</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-2.17718401641647</v>
       </c>
       <c r="E75">
-        <v>-10.47331637895337</v>
+        <v>-9.020935138265315</v>
       </c>
       <c r="F75">
-        <v>-0.6652379857811095</v>
+        <v>-0.879655089423942</v>
       </c>
       <c r="G75">
-        <v>-1.665493574383658</v>
+        <v>0.2749562090958345</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-2.206683809363883</v>
       </c>
       <c r="E76">
-        <v>-10.94970731608628</v>
+        <v>-10.48980002434129</v>
       </c>
       <c r="F76">
-        <v>-0.9810911629989498</v>
+        <v>-1.463842147798029</v>
       </c>
       <c r="G76">
-        <v>-3.021181835988444</v>
+        <v>0.1654897102942935</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-2.222566919904001</v>
       </c>
       <c r="E77">
-        <v>-11.80358278955058</v>
+        <v>-10.84254550716877</v>
       </c>
       <c r="F77">
-        <v>-1.044181281130966</v>
+        <v>-1.423862651836716</v>
       </c>
       <c r="G77">
-        <v>-0.7257223910596672</v>
+        <v>-0.1003338543270258</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-2.222666844687213</v>
       </c>
       <c r="E78">
-        <v>-11.39807152758572</v>
+        <v>-11.65085094669388</v>
       </c>
       <c r="F78">
-        <v>-0.2737606632594939</v>
+        <v>-1.473652502949383</v>
       </c>
       <c r="G78">
-        <v>-1.978446065302041</v>
+        <v>0.323280242332576</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-2.203565754033221</v>
       </c>
       <c r="E79">
-        <v>-12.32267723657583</v>
+        <v>-12.13210093643703</v>
       </c>
       <c r="F79">
-        <v>-1.59159628212738</v>
+        <v>-1.884490428409229</v>
       </c>
       <c r="G79">
-        <v>-0.5622939999680058</v>
+        <v>0.8757738768360052</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-2.163328626874387</v>
       </c>
       <c r="E80">
-        <v>-13.81929713984481</v>
+        <v>-12.45441054545896</v>
       </c>
       <c r="F80">
-        <v>-1.454109659182538</v>
+        <v>-1.671449243022447</v>
       </c>
       <c r="G80">
-        <v>-1.348601534273541</v>
+        <v>0.4183557996749053</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-2.101975156987803</v>
       </c>
       <c r="E81">
-        <v>-13.81744046550167</v>
+        <v>-12.72449779222443</v>
       </c>
       <c r="F81">
-        <v>-1.052525425979365</v>
+        <v>-1.621733944976032</v>
       </c>
       <c r="G81">
-        <v>-0.689170657760574</v>
+        <v>0.9473909084870588</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-2.019677991822833</v>
       </c>
       <c r="E82">
-        <v>-15.3062985643215</v>
+        <v>-13.19399639191767</v>
       </c>
       <c r="F82">
-        <v>-0.8792599581728066</v>
+        <v>-1.643471962360296</v>
       </c>
       <c r="G82">
-        <v>-0.7602414493976478</v>
+        <v>1.212320625812775</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-1.916851219514455</v>
       </c>
       <c r="E83">
-        <v>-15.63564995042536</v>
+        <v>-14.83365267519293</v>
       </c>
       <c r="F83">
-        <v>-1.933607645190823</v>
+        <v>-1.907958076930539</v>
       </c>
       <c r="G83">
-        <v>-0.533853103240127</v>
+        <v>1.41697855105052</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-1.794741764561792</v>
       </c>
       <c r="E84">
-        <v>-18.03954056418308</v>
+        <v>-15.97818825283955</v>
       </c>
       <c r="F84">
-        <v>-1.857924685801449</v>
+        <v>-2.291669455050909</v>
       </c>
       <c r="G84">
-        <v>0.284325052971972</v>
+        <v>1.343540719352867</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-1.657798075873505</v>
       </c>
       <c r="E85">
-        <v>-17.95628456955206</v>
+        <v>-16.72556307459146</v>
       </c>
       <c r="F85">
-        <v>-2.101476299368143</v>
+        <v>-2.005339292068844</v>
       </c>
       <c r="G85">
-        <v>-0.2941464323781182</v>
+        <v>2.536797064073313</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-1.509423582308588</v>
       </c>
       <c r="E86">
-        <v>-19.17892273840898</v>
+        <v>-18.55049734341654</v>
       </c>
       <c r="F86">
-        <v>-2.364645309767934</v>
+        <v>-2.320731897010727</v>
       </c>
       <c r="G86">
-        <v>-1.211578054403107</v>
+        <v>1.91000816657756</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-1.35333784980477</v>
       </c>
       <c r="E87">
-        <v>-19.85975616309218</v>
+        <v>-19.65336643171859</v>
       </c>
       <c r="F87">
-        <v>-2.298166340591066</v>
+        <v>-2.619485085932577</v>
       </c>
       <c r="G87">
-        <v>0.323694060524985</v>
+        <v>1.779519703601647</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-1.194817412590121</v>
       </c>
       <c r="E88">
-        <v>-22.65615226146473</v>
+        <v>-20.53803552843505</v>
       </c>
       <c r="F88">
-        <v>-2.146622322820716</v>
+        <v>-2.05295136527955</v>
       </c>
       <c r="G88">
-        <v>-1.164472301924817</v>
+        <v>2.684646027857164</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-1.041807772417614</v>
       </c>
       <c r="E89">
-        <v>-22.24053344551475</v>
+        <v>-22.02744610108383</v>
       </c>
       <c r="F89">
-        <v>-1.959238161000842</v>
+        <v>-2.504815014730444</v>
       </c>
       <c r="G89">
-        <v>0.422808483425225</v>
+        <v>1.388736287054997</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-0.9007899129059812</v>
       </c>
       <c r="E90">
-        <v>-24.21953998550281</v>
+        <v>-24.55779435150574</v>
       </c>
       <c r="F90">
-        <v>-1.813040426448161</v>
+        <v>-3.080676152338993</v>
       </c>
       <c r="G90">
-        <v>-0.5975182045058512</v>
+        <v>1.943639998711016</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-0.7783507446465988</v>
       </c>
       <c r="E91">
-        <v>-24.91150892777087</v>
+        <v>-24.72805591724613</v>
       </c>
       <c r="F91">
-        <v>-2.138395806143514</v>
+        <v>-2.820055200070213</v>
       </c>
       <c r="G91">
-        <v>0.2308597425127423</v>
+        <v>1.375785432905368</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-0.6821563819095751</v>
       </c>
       <c r="E92">
-        <v>-26.72343289077191</v>
+        <v>-26.2848818824471</v>
       </c>
       <c r="F92">
-        <v>-2.671835420687298</v>
+        <v>-3.22719777854617</v>
       </c>
       <c r="G92">
-        <v>-1.056224083881728</v>
+        <v>0.8009456160118585</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-0.6190267027476597</v>
       </c>
       <c r="E93">
-        <v>-29.174768326708</v>
+        <v>-29.22813186441439</v>
       </c>
       <c r="F93">
-        <v>-3.030391765886855</v>
+        <v>-3.322411984558751</v>
       </c>
       <c r="G93">
-        <v>0.5228928961684716</v>
+        <v>0.9901168092168927</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-0.5918235007615625</v>
       </c>
       <c r="E94">
-        <v>-31.07056642104212</v>
+        <v>-30.6911119985174</v>
       </c>
       <c r="F94">
-        <v>-3.097140782837037</v>
+        <v>-3.252389259632706</v>
       </c>
       <c r="G94">
-        <v>-0.589433852298951</v>
+        <v>1.33262585070989</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-0.60253989261887</v>
       </c>
       <c r="E95">
-        <v>-34.16965477903537</v>
+        <v>-33.76767346255949</v>
       </c>
       <c r="F95">
-        <v>-3.365762935849457</v>
+        <v>-3.332267899917259</v>
       </c>
       <c r="G95">
-        <v>-1.170964281727328</v>
+        <v>0.6702982468500605</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-0.6538435174133848</v>
       </c>
       <c r="E96">
-        <v>-36.7262183654877</v>
+        <v>-34.69955190080591</v>
       </c>
       <c r="F96">
-        <v>-2.914419501127521</v>
+        <v>-3.769745292683734</v>
       </c>
       <c r="G96">
-        <v>-1.469188155541494</v>
+        <v>0.5417001053770711</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-0.7422421550132533</v>
       </c>
       <c r="E97">
-        <v>-37.80377101984986</v>
+        <v>-36.98419647275666</v>
       </c>
       <c r="F97">
-        <v>-3.161335114716984</v>
+        <v>-3.838542862221039</v>
       </c>
       <c r="G97">
-        <v>-2.761797282441008</v>
+        <v>0.1058204374944696</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-0.8665730418653906</v>
       </c>
       <c r="E98">
-        <v>-41.01013666284782</v>
+        <v>-38.48641130566212</v>
       </c>
       <c r="F98">
-        <v>-3.467936256412957</v>
+        <v>-3.619526662757864</v>
       </c>
       <c r="G98">
-        <v>-2.515853543783012</v>
+        <v>-0.1650186036188455</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-1.017451994318332</v>
       </c>
       <c r="E99">
-        <v>-42.79445278406111</v>
+        <v>-41.14871928866756</v>
       </c>
       <c r="F99">
-        <v>-3.836405674321816</v>
+        <v>-3.747616285885348</v>
       </c>
       <c r="G99">
-        <v>-3.182322640112469</v>
+        <v>0.1835255623922429</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-1.199409051318134</v>
       </c>
       <c r="E100">
-        <v>-45.08003701436844</v>
+        <v>-44.18237572572398</v>
       </c>
       <c r="F100">
-        <v>-3.76574344976081</v>
+        <v>-4.242321440674227</v>
       </c>
       <c r="G100">
-        <v>-3.452843868854014</v>
+        <v>-1.45140059435899</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-1.394113288018337</v>
       </c>
       <c r="E101">
-        <v>-46.76158394645166</v>
+        <v>-44.97638024433287</v>
       </c>
       <c r="F101">
-        <v>-3.743507583567463</v>
+        <v>-4.210790463854067</v>
       </c>
       <c r="G101">
-        <v>-2.674488264933808</v>
+        <v>-1.38371980135413</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-1.619962979647723</v>
       </c>
       <c r="E102">
-        <v>-46.19836631293268</v>
+        <v>-47.58322800616637</v>
       </c>
       <c r="F102">
-        <v>-4.461112324203841</v>
+        <v>-4.345819320714803</v>
       </c>
       <c r="G102">
-        <v>-4.460749389921745</v>
+        <v>-1.218864565135042</v>
       </c>
     </row>
   </sheetData>
